--- a/Manuel Validation/CAS S02/Cas S02B.xlsx
+++ b/Manuel Validation/CAS S02/Cas S02B.xlsx
@@ -527,7 +527,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.00000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -808,7 +808,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -962,7 +962,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -974,7 +974,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -994,6 +994,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2196,8 +2199,8 @@
         <v>86</v>
       </c>
       <c r="E56" s="61">
-        <f>hw*tw*FyW/SQRT(3)/GammaM0/1000</f>
-        <v>2428.1702749917972</v>
+        <f>hw*tw*FyW/SQRT(3)/GammaM0/1000*Eta</f>
+        <v>2913.8043299901565</v>
       </c>
       <c r="F56" t="s">
         <v>13</v>
@@ -2233,7 +2236,7 @@
       </c>
       <c r="E58" s="60">
         <f>VEd_U1/VRd</f>
-        <v>0.15764957010739009</v>
+        <v>0.13137464175615843</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>26</v>
@@ -2252,7 +2255,7 @@
       </c>
       <c r="E59" s="60">
         <f>VEd_U2/VRd</f>
-        <v>0.13096280902338048</v>
+        <v>0.1091356741861504</v>
       </c>
       <c r="M59" s="3"/>
     </row>
@@ -2262,7 +2265,7 @@
       </c>
       <c r="E60" s="75">
         <f>MAX(E58:E59)</f>
-        <v>0.15764957010739009</v>
+        <v>0.13137464175615843</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>115</v>
@@ -2468,7 +2471,7 @@
       <c r="D76" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E76" s="75">
+      <c r="E76" s="81">
         <f>MAX(E74:E75)</f>
         <v>0.21474822331883595</v>
       </c>

--- a/Manuel Validation/CAS S02/Cas S02B.xlsx
+++ b/Manuel Validation/CAS S02/Cas S02B.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="9150"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="21570" windowHeight="9150"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="142">
   <si>
     <t xml:space="preserve">PRS </t>
   </si>
@@ -517,6 +517,9 @@
   </si>
   <si>
     <t>GLT</t>
+  </si>
+  <si>
+    <t>NtRd</t>
   </si>
 </sst>
 </file>
@@ -808,7 +811,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -997,6 +1000,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1284,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C4:S99"/>
+  <dimension ref="C4:S111"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
@@ -2702,7 +2708,7 @@
       <c r="D96" s="3"/>
       <c r="E96" s="4"/>
     </row>
-    <row r="97" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D97" s="3" t="s">
         <v>140</v>
       </c>
@@ -2711,12 +2717,39 @@
         <v>1.0677156152368201</v>
       </c>
     </row>
-    <row r="98" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D98" s="3"/>
       <c r="E98" s="4"/>
     </row>
-    <row r="99" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:5" x14ac:dyDescent="0.25">
       <c r="D99" s="3"/>
+    </row>
+    <row r="108" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C108" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D108" s="4">
+        <f>bfs*tfs*FyS/1000</f>
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="109" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D109" s="4">
+        <f>hw*tw*FyW/1000</f>
+        <v>4416</v>
+      </c>
+    </row>
+    <row r="110" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D110" s="4">
+        <f>bfi*tfi*FyI/1000</f>
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="111" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D111" s="82">
+        <f>SUM(D108:D110)/GammaM0</f>
+        <v>9234.2857142857138</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
